--- a/backend/scripts/fixtures/demo_supplier.xlsx
+++ b/backend/scripts/fixtures/demo_supplier.xlsx
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Taxable Amount BDT</t>
+          <t>Taxable Amount (BDT)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>VAT Amount BDT</t>
+          <t>VAT Amount (BDT)</t>
         </is>
       </c>
     </row>

--- a/backend/scripts/fixtures/demo_supplier.xlsx
+++ b/backend/scripts/fixtures/demo_supplier.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -474,7 +474,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>234567890</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>345678901</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>456789012</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>567890123</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>234567890</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>345678901</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>456789012</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>567890123</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>234567890</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>345678901</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>456789012</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>567890123</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>234567890</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>345678901</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>456789012</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>567890123</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>123456789</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>234567890</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -952,12 +952,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INV-0023</t>
+          <t>INV-0023-A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>345678901</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -969,18 +969,18 @@
         <v>15750</v>
       </c>
       <c r="E24" t="n">
-        <v>2480.62</v>
+        <v>2362.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INV-0024</t>
+          <t>INV-0024-A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>456789012</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -992,7 +992,7 @@
         <v>16000</v>
       </c>
       <c r="E25" t="n">
-        <v>2520</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="26">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>234567890</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>345678901</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>456789012</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>567890123</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>234567890</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>999888777</t>
+          <t>345678901</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
